--- a/outputs/evaluation/architecture/validation/CF_M06/CF_M06_arch_eval_avg.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M06/CF_M06_arch_eval_avg.xlsx
@@ -447,10 +447,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9079</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6481</v>
+        <v>0.6296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -465,13 +465,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9688</v>
+        <v>0.916</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7012</v>
+        <v>0.6552</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9557</v>
+        <v>0.9455</v>
       </c>
     </row>
     <row r="4">
@@ -481,13 +481,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6333</v>
+        <v>0.6445</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5</v>
+        <v>0.5238</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8845</v>
+        <v>0.8844</v>
       </c>
     </row>
     <row r="7">
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8847</v>
+        <v>0.8552</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -529,10 +529,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8001</v>
+        <v>0.7691</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8704</v>
+        <v>0.8516</v>
       </c>
     </row>
     <row r="10">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9312</v>
+        <v>0.8961</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1983</v>
+        <v>0.1787</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -641,13 +641,13 @@
         <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>15.6667</v>
+        <v>14.6667</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9815</v>
+        <v>0.9183</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6528</v>
+        <v>0.6111</v>
       </c>
     </row>
     <row r="3">
@@ -660,16 +660,16 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>4.6667</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6667</v>
+        <v>4.3333</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9333</v>
+        <v>0.9167</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9333</v>
+        <v>0.8667</v>
       </c>
     </row>
     <row r="4">
@@ -682,16 +682,16 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>4.6667</v>
+        <v>5.6667</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>3.6667</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6333</v>
+        <v>0.6445</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4286</v>
+        <v>0.5238</v>
       </c>
     </row>
   </sheetData>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25.6667</v>
+        <v>26.3333</v>
       </c>
     </row>
     <row r="4">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.3333</v>
+        <v>22.6667</v>
       </c>
     </row>
     <row r="5">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.3333</v>
+        <v>22.6667</v>
       </c>
     </row>
     <row r="6">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.3333</v>
+        <v>3.6667</v>
       </c>
     </row>
     <row r="7">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12.6667</v>
+        <v>13.3333</v>
       </c>
     </row>
     <row r="8">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9079</v>
+        <v>0.8564000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6481</v>
+        <v>0.6296</v>
       </c>
     </row>
     <row r="10">

--- a/outputs/evaluation/architecture/validation/CF_M06/CF_M06_arch_eval_avg.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M06/CF_M06_arch_eval_avg.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,6 +436,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -452,7 +457,10 @@
       <c r="C2" t="n">
         <v>0.6296</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.7206</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -471,6 +479,9 @@
         <v>0.6552</v>
       </c>
       <c r="D3" t="n">
+        <v>0.7568</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9455</v>
       </c>
     </row>
@@ -487,6 +498,9 @@
         <v>0.5238</v>
       </c>
       <c r="D4" t="n">
+        <v>0.5769</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.8844</v>
       </c>
     </row>
